--- a/data/employee-equity.xlsx
+++ b/data/employee-equity.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q3"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -473,166 +473,113 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>eq-rsu</v>
+        <v>eq-anthropic-iso</v>
       </c>
       <c r="B2" t="str">
-        <v>TechCorp RSUs</v>
+        <v>Anthropic ISOs (Vested)</v>
       </c>
       <c r="C2" t="str">
-        <v>TCORP</v>
+        <v>ANTH-PRIV</v>
       </c>
       <c r="D2">
-        <v>500</v>
+        <v>75000</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>185</v>
+        <v>40</v>
       </c>
       <c r="G2" t="str">
-        <v>Vesting quarterly over 4 years. Next vest: Apr 2026.</v>
+        <v>Initial grant: 120K ISOs over 4 years (joined Jan 2022). ~90K vested, sold ~15K through 2024 tender offer. Holding 75K. Strike $3, 409A FMV $40. AMT exposure on exercise.</v>
       </c>
       <c r="H2" t="str">
         <v>taxable</v>
       </c>
       <c r="I2" t="str">
-        <v>E*TRADE Equity</v>
+        <v>Carta (Anthropic Equity)</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>225000</v>
       </c>
       <c r="K2" t="str">
-        <v>2024-03-01</v>
+        <v>2022-01-15</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-02-11</v>
+        <v>2026-02-12</v>
       </c>
       <c r="M2" t="str">
-        <v>RSU</v>
+        <v>ISO</v>
       </c>
       <c r="N2" t="str">
-        <v>2024-03-01</v>
+        <v>2022-01-15</v>
       </c>
       <c r="O2" t="str">
-        <v>4yr quarterly</v>
+        <v>4yr with 1yr cliff, monthly after</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q2">
-        <v>165</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>eq-iso</v>
+        <v>eq-anthropic-refresh</v>
       </c>
       <c r="B3" t="str">
-        <v>TechCorp ISOs</v>
+        <v>Anthropic RSUs (Refresh)</v>
       </c>
       <c r="C3" t="str">
-        <v>TCORP</v>
+        <v>ANTH-PRIV</v>
       </c>
       <c r="D3">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="E3">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>185</v>
+        <v>40</v>
       </c>
       <c r="G3" t="str">
-        <v>ISO grant. Strike $120. Exercisable after 1yr cliff.</v>
+        <v>Refresh grants 2023-2025. ~8K vested and held. Additional ~12K unvested over next 2-3 years.</v>
       </c>
       <c r="H3" t="str">
         <v>taxable</v>
       </c>
       <c r="I3" t="str">
-        <v>E*TRADE Equity</v>
+        <v>Carta (Anthropic Equity)</v>
       </c>
       <c r="J3">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="K3" t="str">
-        <v>2023-06-15</v>
+        <v>2023-06-01</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-02-11</v>
+        <v>2026-02-12</v>
       </c>
       <c r="M3" t="str">
-        <v>ISO</v>
+        <v>RSU</v>
       </c>
       <c r="N3" t="str">
-        <v>2023-06-15</v>
+        <v>2023-06-01</v>
       </c>
       <c r="O3" t="str">
-        <v>4yr with 1yr cliff</v>
+        <v>4yr quarterly</v>
       </c>
       <c r="P3">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>eq-espp</v>
-      </c>
-      <c r="B4" t="str">
-        <v>TechCorp ESPP</v>
-      </c>
-      <c r="C4" t="str">
-        <v>TCORP</v>
-      </c>
-      <c r="D4">
-        <v>200</v>
-      </c>
-      <c r="E4">
-        <v>140</v>
-      </c>
-      <c r="F4">
-        <v>185</v>
-      </c>
-      <c r="G4" t="str">
-        <v>ESPP shares purchased at 15% discount. 6-month lookback.</v>
-      </c>
-      <c r="H4" t="str">
-        <v>taxable</v>
-      </c>
-      <c r="I4" t="str">
-        <v>E*TRADE Equity</v>
-      </c>
-      <c r="J4">
-        <v>28000</v>
-      </c>
-      <c r="K4" t="str">
-        <v>2025-06-30</v>
-      </c>
-      <c r="L4" t="str">
-        <v>2026-02-11</v>
-      </c>
-      <c r="M4" t="str">
-        <v>ESPP</v>
-      </c>
-      <c r="N4" t="str">
-        <v>2025-01-01</v>
-      </c>
-      <c r="O4" t="str">
-        <v>6mo purchase period</v>
-      </c>
-      <c r="P4">
-        <v>140</v>
-      </c>
-      <c r="Q4">
-        <v>165</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/employee-equity.xlsx
+++ b/data/employee-equity.xlsx
@@ -473,108 +473,108 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>eq-anthropic-iso</v>
+        <v>eq-googl-rsu</v>
       </c>
       <c r="B2" t="str">
-        <v>Anthropic ISOs (Vested)</v>
+        <v>Google RSUs</v>
       </c>
       <c r="C2" t="str">
-        <v>ANTH-PRIV</v>
+        <v>GOOGL</v>
       </c>
       <c r="D2">
-        <v>75000</v>
+        <v>2000</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>40</v>
+        <v>185</v>
       </c>
       <c r="G2" t="str">
-        <v>Initial grant: 120K ISOs over 4 years (joined Jan 2022). ~90K vested, sold ~15K through 2024 tender offer. Holding 75K. Strike $3, 409A FMV $40. AMT exposure on exercise.</v>
+        <v>L7 initial grant: 6,000 shares over 4 years. ~3,000 vested as of Feb 2026. Holding ~2,000 vested; sold ~1,000 to diversify. Next vest: Apr 2026 (~375 shares).</v>
       </c>
       <c r="H2" t="str">
         <v>taxable</v>
       </c>
       <c r="I2" t="str">
-        <v>Carta (Anthropic Equity)</v>
+        <v>E*TRADE Equity</v>
       </c>
       <c r="J2">
-        <v>225000</v>
+        <v>0</v>
       </c>
       <c r="K2" t="str">
-        <v>2022-01-15</v>
+        <v>2024-03-01</v>
       </c>
       <c r="L2" t="str">
         <v>2026-02-12</v>
       </c>
       <c r="M2" t="str">
-        <v>ISO</v>
+        <v>RSU</v>
       </c>
       <c r="N2" t="str">
-        <v>2022-01-15</v>
+        <v>2024-03-01</v>
       </c>
       <c r="O2" t="str">
-        <v>4yr with 1yr cliff, monthly after</v>
+        <v>4yr quarterly (~375 shares/quarter)</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>5</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>eq-anthropic-refresh</v>
+        <v>eq-googl-espp</v>
       </c>
       <c r="B3" t="str">
-        <v>Anthropic RSUs (Refresh)</v>
+        <v>Google ESPP</v>
       </c>
       <c r="C3" t="str">
-        <v>ANTH-PRIV</v>
+        <v>GOOGL</v>
       </c>
       <c r="D3">
-        <v>8000</v>
+        <v>200</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>185</v>
       </c>
       <c r="G3" t="str">
-        <v>Refresh grants 2023-2025. ~8K vested and held. Additional ~12K unvested over next 2-3 years.</v>
+        <v>ESPP shares purchased at 15% discount. 6-month lookback.</v>
       </c>
       <c r="H3" t="str">
         <v>taxable</v>
       </c>
       <c r="I3" t="str">
-        <v>Carta (Anthropic Equity)</v>
+        <v>E*TRADE Equity</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="K3" t="str">
-        <v>2023-06-01</v>
+        <v>2025-06-30</v>
       </c>
       <c r="L3" t="str">
         <v>2026-02-12</v>
       </c>
       <c r="M3" t="str">
-        <v>RSU</v>
+        <v>ESPP</v>
       </c>
       <c r="N3" t="str">
-        <v>2023-06-01</v>
+        <v>2025-01-01</v>
       </c>
       <c r="O3" t="str">
-        <v>4yr quarterly</v>
+        <v>6mo purchase period</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="Q3">
-        <v>20</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/data/employee-equity.xlsx
+++ b/data/employee-equity.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:S4"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -416,6 +416,8 @@
     <col min="15" max="15" width="20.83203125" customWidth="1"/>
     <col min="16" max="16" width="12.83203125" customWidth="1"/>
     <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,116 +472,193 @@
       <c r="Q1" t="str">
         <v>fmvAtGrant</v>
       </c>
+      <c r="R1" t="str">
+        <v>fmvAtExercise</v>
+      </c>
+      <c r="S1" t="str">
+        <v>fmvAtVest</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>eq-googl-rsu</v>
+        <v>eq-anthropic-iso-exercised</v>
       </c>
       <c r="B2" t="str">
-        <v>Google RSUs</v>
+        <v>Anthropic ISOs (Exercised)</v>
       </c>
       <c r="C2" t="str">
-        <v>GOOGL</v>
+        <v>ANTH-PRIV</v>
       </c>
       <c r="D2">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>185</v>
+        <v>40</v>
       </c>
       <c r="G2" t="str">
-        <v>L7 initial grant: 6,000 shares over 4 years. ~3,000 vested as of Feb 2026. Holding ~2,000 vested; sold ~1,000 to diversify. Next vest: Apr 2026 (~375 shares).</v>
+        <v>Exercised Mar 2025 (batch 1). 15K shares at $3 strike, FMV $40 at exercise. Cost basis $45K. Holding for qualifying disposition (need 1yr from exercise + 2yr from grant). AMT preference $555K already recognized.</v>
       </c>
       <c r="H2" t="str">
         <v>taxable</v>
       </c>
       <c r="I2" t="str">
-        <v>E*TRADE Equity</v>
+        <v>Carta (Anthropic Equity)</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="K2" t="str">
-        <v>2024-03-01</v>
+        <v>2025-03-15</v>
       </c>
       <c r="L2" t="str">
         <v>2026-02-12</v>
       </c>
       <c r="M2" t="str">
-        <v>RSU</v>
+        <v>ISO</v>
       </c>
       <c r="N2" t="str">
-        <v>2024-03-01</v>
+        <v>2022-01-15</v>
       </c>
       <c r="O2" t="str">
-        <v>4yr quarterly (~375 shares/quarter)</v>
+        <v>Exercised</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q2">
-        <v>165</v>
+        <v>5</v>
+      </c>
+      <c r="R2">
+        <v>40</v>
+      </c>
+      <c r="S2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>eq-googl-espp</v>
+        <v>eq-anthropic-iso-unexercised</v>
       </c>
       <c r="B3" t="str">
-        <v>Google ESPP</v>
+        <v>Anthropic ISOs (Unexercised)</v>
       </c>
       <c r="C3" t="str">
-        <v>GOOGL</v>
+        <v>ANTH-PRIV</v>
       </c>
       <c r="D3">
-        <v>200</v>
+        <v>105000</v>
       </c>
       <c r="E3">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>185</v>
+        <v>40</v>
       </c>
       <c r="G3" t="str">
-        <v>ESPP shares purchased at 15% discount. 6-month lookback.</v>
+        <v>105K fully vested ISOs. Strike $3, current FMV $40. Exercise requires $315K cash outlay + triggers AMT. Spread at current FMV: $3.885M. Recommended pace: 15K/year over 7 years. Vesting expiry: Jan 2032.</v>
       </c>
       <c r="H3" t="str">
         <v>taxable</v>
       </c>
       <c r="I3" t="str">
-        <v>E*TRADE Equity</v>
+        <v>Carta (Anthropic Equity)</v>
       </c>
       <c r="J3">
-        <v>31000</v>
+        <v>315000</v>
       </c>
       <c r="K3" t="str">
-        <v>2025-06-30</v>
+        <v>2022-01-15</v>
       </c>
       <c r="L3" t="str">
         <v>2026-02-12</v>
       </c>
       <c r="M3" t="str">
-        <v>ESPP</v>
+        <v>ISO</v>
       </c>
       <c r="N3" t="str">
-        <v>2025-01-01</v>
+        <v>2022-01-15</v>
       </c>
       <c r="O3" t="str">
-        <v>6mo purchase period</v>
+        <v>Fully vested</v>
       </c>
       <c r="P3">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="Q3">
-        <v>178</v>
+        <v>5</v>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>eq-anthropic-refresh</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Anthropic RSUs (Refresh)</v>
+      </c>
+      <c r="C4" t="str">
+        <v>ANTH-PRIV</v>
+      </c>
+      <c r="D4">
+        <v>8000</v>
+      </c>
+      <c r="E4">
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>40</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Refresh grants 2023-2025. 20K total, ~10K vested (avg FMV ~$25 at vest, already taxed as W-2). Sold 2K in Nov 2025 tender at $45/share ($90K). 8K held. Unrealized cap gain: ($40-$25)×8K = $120K.</v>
+      </c>
+      <c r="H4" t="str">
+        <v>taxable</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Carta (Anthropic Equity)</v>
+      </c>
+      <c r="J4">
+        <v>200000</v>
+      </c>
+      <c r="K4" t="str">
+        <v>2023-06-01</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-02-12</v>
+      </c>
+      <c r="M4" t="str">
+        <v>RSU</v>
+      </c>
+      <c r="N4" t="str">
+        <v>2023-06-01</v>
+      </c>
+      <c r="O4" t="str">
+        <v>4yr quarterly</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>20</v>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/employee-equity.xlsx
+++ b/data/employee-equity.xlsx
@@ -398,27 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:S4"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="20.83203125" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
-    <col min="18" max="18" width="14.83203125" customWidth="1"/>
-    <col min="19" max="19" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -496,7 +475,7 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G2" t="str">
         <v>Exercised Mar 2025 (batch 1). 15K shares at $3 strike, FMV $40 at exercise. Cost basis $45K. Holding for qualifying disposition (need 1yr from exercise + 2yr from grant). AMT preference $555K already recognized.</v>
@@ -514,7 +493,7 @@
         <v>2025-03-15</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
       <c r="M2" t="str">
         <v>ISO</v>
@@ -555,7 +534,7 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G3" t="str">
         <v>105K fully vested ISOs. Strike $3, current FMV $40. Exercise requires $315K cash outlay + triggers AMT. Spread at current FMV: $3.885M. Recommended pace: 15K/year over 7 years. Vesting expiry: Jan 2032.</v>
@@ -573,7 +552,7 @@
         <v>2022-01-15</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
       <c r="M3" t="str">
         <v>ISO</v>
@@ -614,7 +593,7 @@
         <v>25</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G4" t="str">
         <v>Refresh grants 2023-2025. 20K total, ~10K vested (avg FMV ~$25 at vest, already taxed as W-2). Sold 2K in Nov 2025 tender at $45/share ($90K). 8K held. Unrealized cap gain: ($40-$25)×8K = $120K.</v>
@@ -632,7 +611,7 @@
         <v>2023-06-01</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
       <c r="M4" t="str">
         <v>RSU</v>

--- a/data/employee-equity.xlsx
+++ b/data/employee-equity.xlsx
@@ -397,7 +397,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S3"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="10.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,58 +481,58 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>eq-anthropic-iso-exercised</v>
+        <v>eq-googl-rsu</v>
       </c>
       <c r="B2" t="str">
-        <v>Anthropic ISOs (Exercised)</v>
+        <v>Google RSUs</v>
       </c>
       <c r="C2" t="str">
-        <v>ANTH-PRIV</v>
+        <v>GOOGL</v>
       </c>
       <c r="D2">
-        <v>15000</v>
+        <v>2000</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>185</v>
       </c>
       <c r="G2" t="str">
-        <v>Exercised Mar 2025 (batch 1). 15K shares at $3 strike, FMV $40 at exercise. Cost basis $45K. Holding for qualifying disposition (need 1yr from exercise + 2yr from grant). AMT preference $555K already recognized.</v>
+        <v>L7 initial grant: 6,000 shares over 4 years. ~3,000 vested as of Feb 2026. Holding ~2,000 vested; sold ~1,000 to diversify. Next vest: Apr 2026 (~375 shares).</v>
       </c>
       <c r="H2" t="str">
         <v>taxable</v>
       </c>
       <c r="I2" t="str">
-        <v>Carta (Anthropic Equity)</v>
+        <v>E*TRADE Equity</v>
       </c>
       <c r="J2">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="K2" t="str">
-        <v>2025-03-15</v>
+        <v>2024-03-01</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
       <c r="M2" t="str">
-        <v>ISO</v>
+        <v>RSU</v>
       </c>
       <c r="N2" t="str">
-        <v>2022-01-15</v>
+        <v>2024-03-01</v>
       </c>
       <c r="O2" t="str">
-        <v>Exercised</v>
+        <v>4yr quarterly (~375 shares/quarter)</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>5</v>
-      </c>
-      <c r="R2">
-        <v>40</v>
+        <v>165</v>
+      </c>
+      <c r="R2" t="str">
+        <v/>
       </c>
       <c r="S2" t="str">
         <v/>
@@ -519,125 +540,66 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>eq-anthropic-iso-unexercised</v>
+        <v>eq-googl-espp</v>
       </c>
       <c r="B3" t="str">
-        <v>Anthropic ISOs (Unexercised)</v>
+        <v>Google ESPP</v>
       </c>
       <c r="C3" t="str">
-        <v>ANTH-PRIV</v>
+        <v>GOOGL</v>
       </c>
       <c r="D3">
-        <v>105000</v>
+        <v>200</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>185</v>
       </c>
       <c r="G3" t="str">
-        <v>105K fully vested ISOs. Strike $3, current FMV $40. Exercise requires $315K cash outlay + triggers AMT. Spread at current FMV: $3.885M. Recommended pace: 15K/year over 7 years. Vesting expiry: Jan 2032.</v>
+        <v>ESPP shares purchased at 15% discount. 6-month lookback.</v>
       </c>
       <c r="H3" t="str">
         <v>taxable</v>
       </c>
       <c r="I3" t="str">
-        <v>Carta (Anthropic Equity)</v>
+        <v>E*TRADE Equity</v>
       </c>
       <c r="J3">
-        <v>315000</v>
+        <v>31000</v>
       </c>
       <c r="K3" t="str">
-        <v>2022-01-15</v>
+        <v>2025-06-30</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
       <c r="M3" t="str">
-        <v>ISO</v>
+        <v>ESPP</v>
       </c>
       <c r="N3" t="str">
-        <v>2022-01-15</v>
+        <v>2025-01-01</v>
       </c>
       <c r="O3" t="str">
-        <v>Fully vested</v>
+        <v>6mo purchase period</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>178</v>
       </c>
       <c r="R3" t="str">
         <v/>
       </c>
       <c r="S3" t="str">
         <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>eq-anthropic-refresh</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Anthropic RSUs (Refresh)</v>
-      </c>
-      <c r="C4" t="str">
-        <v>ANTH-PRIV</v>
-      </c>
-      <c r="D4">
-        <v>8000</v>
-      </c>
-      <c r="E4">
-        <v>25</v>
-      </c>
-      <c r="F4">
-        <v>50</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Refresh grants 2023-2025. 20K total, ~10K vested (avg FMV ~$25 at vest, already taxed as W-2). Sold 2K in Nov 2025 tender at $45/share ($90K). 8K held. Unrealized cap gain: ($40-$25)×8K = $120K.</v>
-      </c>
-      <c r="H4" t="str">
-        <v>taxable</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Carta (Anthropic Equity)</v>
-      </c>
-      <c r="J4">
-        <v>200000</v>
-      </c>
-      <c r="K4" t="str">
-        <v>2023-06-01</v>
-      </c>
-      <c r="L4" t="str">
-        <v>2026-02-13</v>
-      </c>
-      <c r="M4" t="str">
-        <v>RSU</v>
-      </c>
-      <c r="N4" t="str">
-        <v>2023-06-01</v>
-      </c>
-      <c r="O4" t="str">
-        <v>4yr quarterly</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>20</v>
-      </c>
-      <c r="R4" t="str">
-        <v/>
-      </c>
-      <c r="S4">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S3"/>
   </ignoredErrors>
 </worksheet>
 </file>